--- a/business_surveys/035_driver_cleaning_kit_survey--business_surveys.xlsx
+++ b/business_surveys/035_driver_cleaning_kit_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -937,7 +937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -999,34 +999,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>vehicle_cleaning_kit_choices</t>
+          <t>vehicle_cleaning_frequency_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ประก</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ประก</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>vehicle_cleaning_kit_choices</t>
+          <t>vehicle_cleaning_frequency_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ประก</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ประก</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1055,46 +1055,46 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>vehicle_cleaning_frequency_choices</t>
+          <t>contact_method_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Weekly</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>vehicle_cleaning_frequency_choices</t>
+          <t>contact_method_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>sms</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>SMS</t>
         </is>
       </c>
     </row>
@@ -1123,46 +1123,46 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>chat</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Chat</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>contact_method_choices</t>
+          <t>vehicle_model_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>sms</t>
+          <t>model_1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SMS</t>
+          <t>Model 1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>contact_method_choices</t>
+          <t>vehicle_model_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>chat</t>
+          <t>model_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chat</t>
+          <t>Model 2</t>
         </is>
       </c>
     </row>
@@ -1174,12 +1174,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>model_1</t>
+          <t>model_3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Model 1</t>
+          <t>Model 3</t>
         </is>
       </c>
     </row>
@@ -1191,46 +1191,46 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>model_2</t>
+          <t>model_4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Model 2</t>
+          <t>Model 4</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>vehicle_model_choices</t>
+          <t>vehicle_type_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>model_3</t>
+          <t>car</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Model 3</t>
+          <t>Car</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>vehicle_model_choices</t>
+          <t>vehicle_type_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>model_4</t>
+          <t>motorcycle</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Model 4</t>
+          <t>Motorcycle</t>
         </is>
       </c>
     </row>
@@ -1242,12 +1242,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>truck</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Truck</t>
         </is>
       </c>
     </row>
@@ -1259,46 +1259,46 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>motorcycle</t>
+          <t>van</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Van</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>vehicle_type_choices</t>
+          <t>vehicle_color_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>truck</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Truck</t>
+          <t>Red</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>vehicle_type_choices</t>
+          <t>vehicle_color_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>van</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Van</t>
+          <t>Blue</t>
         </is>
       </c>
     </row>
@@ -1310,12 +1310,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>green</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Green</t>
         </is>
       </c>
     </row>
@@ -1327,46 +1327,46 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>blue</t>
+          <t>yellow</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Yellow</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>vehicle_color_choices</t>
+          <t>vehicle_condition_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>new</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>New</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>vehicle_color_choices</t>
+          <t>vehicle_condition_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>yellow</t>
+          <t>used</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Used</t>
         </is>
       </c>
     </row>
@@ -1378,12 +1378,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>new</t>
+          <t>reconditioned</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Reconditioned</t>
         </is>
       </c>
     </row>
@@ -1395,46 +1395,46 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>used</t>
+          <t>old</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Used</t>
+          <t>Old</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>vehicle_condition_choices</t>
+          <t>vehicle_status_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>reconditioned</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Reconditioned</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>vehicle_condition_choices</t>
+          <t>vehicle_status_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>old</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -1446,44 +1446,10 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>sold</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>vehicle_status_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>vehicle_status_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>sold</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
         <is>
           <t>Sold</t>
         </is>
